--- a/data/Skill.xlsx
+++ b/data/Skill.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS19"/>
+  <dimension ref="A1:AS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,21 +427,11 @@
           <t>skill_type</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>skill_type</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
           <t>targeting_mode</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>targeting_mode</t>
-        </is>
-      </c>
       <c r="F1" t="inlineStr">
         <is>
           <t>rquest_target</t>
@@ -469,42 +459,12 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>requireditem_type</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>requireditem_value</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>requireditem_type</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>requireditem_value</t>
+          <t>requireditem</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>requiredresource_type</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>requiredresource_value</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>requiredresource_type</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>requiredresource_value</t>
+          <t>requiredresource</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
@@ -512,41 +472,6 @@
           <t>effect</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
       <c r="AA1" t="inlineStr">
         <is>
           <t>channelthink</t>
@@ -569,42 +494,7 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>requestresource_id</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>requestresource_cost</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>requestresource_id</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>requestresource_cost</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>requestresource_id</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>requestresource_cost</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>requestresource_id</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>requestresource_cost</t>
+          <t>requestresource</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
@@ -651,187 +541,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>repeated uint32</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>repeated uint32</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>repeated { uint32 type; uint64 value }</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>repeated { uint32 type; uint32 value }</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>repeated uint32</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>uint64</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>uint64</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>uint32</t>
+          <t>repeated { uint32 id; uint32 cost }</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -871,383 +651,131 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>repeated</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>repeated</t>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>message:requireditem</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>message:requireditem</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>message:requireditem</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>message:requireditem</t>
+          <t>common</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>message:requiredresource</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>message:requiredresource</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>message:requiredresource</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>message:requiredresource</t>
+          <t>common</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>repeated</t>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>message:requestresource</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>message:requestresource</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>message:requestresource</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>message:requestresource</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>message:requestresource</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>message:requestresource</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>message:requestresource</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>message:requestresource</t>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>expr:double expr_params:level</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>expr:double expr_params:level</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>enum eSkillType : uint32_t {
  kPassiveSkill = 1 &lt;&lt; 0,    // 被动技能
@@ -1259,119 +787,220 @@
 };</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>0技能释放时不需要目标即可释放（如群疗，踩地板技能） -&gt; 1 &lt;&lt; 1
 1技能释放时需要选定目标（单体指向性技能） -&gt; 1 &lt;&lt; 2
 2技能释放时需要以指定地点为目标（常用于AOE技能） -&gt; 1 &lt;&lt; 3</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>目标</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>目标状态</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>CastPoint(毫秒Spell时间点）,
 一般为动画抬手到攻击帧时长。比如说播放一个挥刀动画0.3秒后动画到攻击点，这时策划就配置CastPoint为0.3秒。</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>后摇阶段一般不能被其他技能打断，除非是连招或者强制立即释放类技能。我们的技能系统不需要引入公共CD这个概念，通过前摇后摇阶段的划分就足够满足各种需求了</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>技能前摇阶段不允许其他技能释放，除非技能可强制立即释放（bImmediately=true）（如有些游戏要求滚动还有解控技可以立即打断当前技能）</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>资源条件</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>资源数量</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>资源数量</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>资源数量</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>资源条件</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>资源数量</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>资源数量</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>资源数量</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>技能范围</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>最大距离</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>最小距离</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>自身状态</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>所需状态</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>所需状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>100*level</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -1383,13 +1012,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -1452,16 +1081,16 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1491,7 +1120,7 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -1501,16 +1130,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="n">
         <v>2</v>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1631,22 +1260,22 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100*level</t>
+          <t>1000*level</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="n">
         <v>3</v>
       </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1767,22 +1396,22 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>1000*level</t>
+          <t>10000*level</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="n">
         <v>4</v>
       </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1909,16 +1538,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="n">
         <v>5</v>
       </c>
-      <c r="B11" t="n">
-        <v>4</v>
+      <c r="C11" t="n">
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2039,25 +1671,22 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>10000*level</t>
+          <t>100*level</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2178,22 +1807,22 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100*level</t>
+          <t>1000*level</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="n">
         <v>7</v>
       </c>
-      <c r="B13" t="n">
-        <v>6</v>
-      </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2314,22 +1943,22 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>1000*level</t>
+          <t>10000*level</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="n">
         <v>8</v>
       </c>
-      <c r="B14" t="n">
-        <v>7</v>
-      </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2450,23 +2079,17 @@
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>10000*level</t>
+          <t>100*level</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="n">
         <v>9</v>
       </c>
-      <c r="B15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
@@ -2586,16 +2209,22 @@
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>100*level</t>
+          <t>1000*level</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="n">
         <v>10</v>
       </c>
-      <c r="B16" t="n">
-        <v>9</v>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2716,22 +2345,25 @@
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>1000*level</t>
+          <t>10000*level</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="n">
         <v>11</v>
       </c>
-      <c r="B17" t="n">
-        <v>10</v>
+      <c r="C17" t="n">
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2858,13 +2490,13 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -2879,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2912,28 +2544,28 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>1</v>
@@ -2987,148 +2619,9 @@
         <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AS18" t="inlineStr">
-        <is>
-          <t>10000*level</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>13</v>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>14</v>
-      </c>
-      <c r="T19" t="n">
-        <v>16</v>
-      </c>
-      <c r="U19" t="n">
-        <v>19</v>
-      </c>
-      <c r="V19" t="n">
-        <v>20</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS19" t="inlineStr">
         <is>
           <t>10000*level</t>
         </is>

--- a/data/Skill.xlsx
+++ b/data/Skill.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>rquest_target</t>
+          <t>require_target</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -444,27 +444,27 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>castpoint</t>
+          <t>cast_point</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>recoverytime</t>
+          <t>recovery_time</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>immediately</t>
+          <t>immediate</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>requireditem</t>
+          <t>required_item</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>requiredresource</t>
+          <t>required_resource</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
@@ -474,27 +474,27 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>channelthink</t>
+          <t>channel_think</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>channelfinish</t>
+          <t>channel_finish</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>thinkinterval</t>
+          <t>think_interval</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>channeltime</t>
+          <t>channel_time</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>requestresource</t>
+          <t>request_resource</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">

--- a/data/Skill.xlsx
+++ b/data/Skill.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>request_resource</t>
+          <t>cost_resource</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
